--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="185">
   <si>
     <t/>
   </si>
@@ -227,9 +227,6 @@
   </si>
   <si>
     <t>CADBURY CRISP-IT 52G</t>
-  </si>
-  <si>
-    <t>,(E-1B)</t>
   </si>
   <si>
     <t>20057444</t>
@@ -1589,61 +1586,61 @@
         <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>11</v>
@@ -1654,16 +1651,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>4</v>
@@ -1674,16 +1671,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>8</v>
@@ -1694,16 +1691,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>11</v>
@@ -1714,16 +1711,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>4</v>
@@ -1734,16 +1731,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>8</v>
@@ -1754,16 +1751,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>11</v>
@@ -1774,16 +1771,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>14</v>
@@ -1794,16 +1791,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>33</v>
@@ -1814,16 +1811,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>4</v>
@@ -1834,16 +1831,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>8</v>
@@ -1854,16 +1851,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>11</v>
@@ -1874,16 +1871,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>14</v>
@@ -1894,16 +1891,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>4</v>
@@ -1914,16 +1911,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>8</v>
@@ -1934,16 +1931,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>11</v>
@@ -1954,16 +1951,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>14</v>
@@ -1974,16 +1971,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>33</v>
@@ -1994,16 +1991,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>38</v>
@@ -2014,76 +2011,76 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>14</v>
@@ -2094,16 +2091,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>33</v>
@@ -2114,16 +2111,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>4</v>
@@ -2134,16 +2131,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>8</v>
@@ -2154,16 +2151,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>11</v>
@@ -2174,16 +2171,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>14</v>
@@ -2194,16 +2191,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>33</v>
@@ -2214,16 +2211,16 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>38</v>
@@ -2234,16 +2231,16 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="C64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>4</v>
@@ -2254,16 +2251,16 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>8</v>
@@ -2274,16 +2271,16 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>11</v>
@@ -2294,16 +2291,16 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>14</v>
@@ -2314,16 +2311,16 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="C68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>4</v>
@@ -2334,16 +2331,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>8</v>
@@ -2354,36 +2351,36 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>14</v>
@@ -2394,116 +2391,116 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>4</v>
@@ -2514,16 +2511,16 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>8</v>
@@ -2534,16 +2531,16 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>11</v>
@@ -2554,16 +2551,16 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>14</v>
@@ -2574,16 +2571,16 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>33</v>

--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="187">
   <si>
     <t/>
   </si>
@@ -196,70 +196,76 @@
     <t>CADBURY DAIRY MILK25</t>
   </si>
   <si>
+    <t>20142220</t>
+  </si>
+  <si>
+    <t>CADBURY RST ALMD 52G</t>
+  </si>
+  <si>
+    <t>20092067</t>
+  </si>
+  <si>
+    <t>CADBURY LICKABLES 20</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20039717</t>
+  </si>
+  <si>
+    <t>CADBURY DAIRY MLK 52</t>
+  </si>
+  <si>
+    <t>20082194</t>
+  </si>
+  <si>
+    <t>CADBURY OREO 58.5G</t>
+  </si>
+  <si>
+    <t>20141836</t>
+  </si>
+  <si>
+    <t>CADBURY CRISP-IT 52G</t>
+  </si>
+  <si>
+    <t>20057444</t>
+  </si>
+  <si>
+    <t>KINDER/J CHOC GIRL20</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20057442</t>
+  </si>
+  <si>
+    <t>KINDER/J CHOC BOYS20</t>
+  </si>
+  <si>
+    <t>20120946</t>
+  </si>
+  <si>
+    <t>KINDER JOY DC COMICS</t>
+  </si>
+  <si>
     <t>20140012</t>
   </si>
   <si>
     <t>KITKAT CHNKY MILO 38</t>
   </si>
   <si>
-    <t>20092067</t>
-  </si>
-  <si>
-    <t>CADBURY LICKABLES 20</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20039717</t>
-  </si>
-  <si>
-    <t>CADBURY DAIRY MLK 52</t>
-  </si>
-  <si>
-    <t>20082194</t>
-  </si>
-  <si>
-    <t>CADBURY OREO 58.5G</t>
-  </si>
-  <si>
-    <t>20141836</t>
-  </si>
-  <si>
-    <t>CADBURY CRISP-IT 52G</t>
-  </si>
-  <si>
-    <t>20057444</t>
-  </si>
-  <si>
-    <t>KINDER/J CHOC GIRL20</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20057442</t>
-  </si>
-  <si>
-    <t>KINDER/J CHOC BOYS20</t>
-  </si>
-  <si>
-    <t>20120946</t>
-  </si>
-  <si>
-    <t>KINDER JOY DC COMICS</t>
+    <t>11</t>
   </si>
   <si>
     <t>20139949</t>
   </si>
   <si>
     <t>LMNILO CRNCHY CHO 18</t>
-  </si>
-  <si>
-    <t>11</t>
   </si>
   <si>
     <t>20129814</t>
@@ -958,7 +964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1720,10 +1726,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1731,19 +1737,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1760,10 +1766,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -1780,10 +1786,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -1800,10 +1806,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -1820,10 +1826,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -1831,19 +1837,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -1860,10 +1866,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -1880,10 +1886,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -1900,10 +1906,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -1911,19 +1917,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="E48" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -1940,10 +1946,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -1960,10 +1966,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -1980,10 +1986,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2000,10 +2006,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2020,30 +2026,30 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>75</v>
@@ -2060,10 +2066,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>75</v>
@@ -2080,13 +2086,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2100,10 +2106,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2120,10 +2126,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2131,19 +2137,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2160,10 +2166,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2180,10 +2186,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2200,10 +2206,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2220,10 +2226,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2240,10 +2246,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2251,19 +2257,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2280,10 +2286,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2300,10 +2306,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2320,10 +2326,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2331,19 +2337,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2360,33 +2366,33 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2400,33 +2406,33 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="C73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2440,13 +2446,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2460,13 +2466,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2480,13 +2486,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2500,30 +2506,30 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>162</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2540,10 +2546,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2560,10 +2566,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2580,12 +2586,32 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E81" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F82" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="185">
   <si>
     <t/>
   </si>
@@ -500,12 +500,6 @@
   </si>
   <si>
     <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20134164</t>
-  </si>
-  <si>
-    <t>CHP.CHUP KRT NNAS 20</t>
   </si>
   <si>
     <t>10035551</t>
@@ -964,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2406,30 +2400,30 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="E73" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>162</v>
@@ -2446,10 +2440,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>162</v>
@@ -2466,10 +2460,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>162</v>
@@ -2486,10 +2480,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>162</v>
@@ -2506,30 +2500,30 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>162</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2546,10 +2540,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2566,10 +2560,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2586,32 +2580,12 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F82" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -490,7 +490,7 @@
     <t>20115133</t>
   </si>
   <si>
-    <t>FSHRMAN'S CHO.MINT25</t>
+    <t>FSHRMAN'S CHO.MINT22</t>
   </si>
   <si>
     <t>10035320</t>

--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="187">
   <si>
     <t/>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>JLO CHOCOEGG DRMON25</t>
+  </si>
+  <si>
+    <t>20142332</t>
+  </si>
+  <si>
+    <t>LARIST CHOCO EGG 20G</t>
   </si>
   <si>
     <t>20135198</t>
@@ -958,7 +964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1740,10 +1746,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1751,19 +1757,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -1780,10 +1786,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -1800,10 +1806,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -1820,10 +1826,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -1840,10 +1846,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -1851,19 +1857,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -1880,10 +1886,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -1900,10 +1906,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -1920,10 +1926,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -1931,19 +1937,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -1960,10 +1966,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -1980,10 +1986,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2000,10 +2006,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2020,10 +2026,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2040,30 +2046,30 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>75</v>
@@ -2080,10 +2086,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>75</v>
@@ -2100,13 +2106,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2120,10 +2126,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2140,10 +2146,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2151,19 +2157,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2180,10 +2186,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2200,10 +2206,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2220,10 +2226,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2240,10 +2246,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2260,10 +2266,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2271,19 +2277,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2300,10 +2306,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2320,10 +2326,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2340,10 +2346,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2351,19 +2357,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2380,53 +2386,53 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>162</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="C73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2440,13 +2446,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2460,13 +2466,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2480,13 +2486,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2500,30 +2506,30 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2540,10 +2546,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2560,10 +2566,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2580,12 +2586,32 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E81" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F82" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="190">
   <si>
     <t/>
   </si>
@@ -383,6 +383,15 @@
   </si>
   <si>
     <t>FSHERMAN'S BLKCRN 22</t>
+  </si>
+  <si>
+    <t>20142507</t>
+  </si>
+  <si>
+    <t>FSHRMANS COLA 25</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
   </si>
   <si>
     <t>20132839</t>
@@ -964,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2066,13 +2075,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2086,10 +2095,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>75</v>
@@ -2097,19 +2106,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="E57" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>75</v>
@@ -2117,39 +2126,39 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2157,19 +2166,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2186,10 +2195,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2197,19 +2206,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2217,19 +2226,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2237,19 +2246,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2257,19 +2266,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2277,19 +2286,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2306,10 +2315,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2317,19 +2326,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2337,19 +2346,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2357,19 +2366,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2386,10 +2395,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2397,22 +2406,22 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>164</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2426,13 +2435,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2446,93 +2455,93 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
+      <c r="E75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2546,10 +2555,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2557,19 +2566,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2577,19 +2586,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2597,21 +2606,41 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E82" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F83" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="187">
   <si>
     <t/>
   </si>
@@ -109,7 +109,7 @@
     <t>10003485</t>
   </si>
   <si>
-    <t>S/Q CHOCO ALMOND 52G</t>
+    <t>S/Q CHOCO ALMND 52 G</t>
   </si>
   <si>
     <t>5</t>
@@ -118,7 +118,7 @@
     <t>10036987</t>
   </si>
   <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
+    <t>S/Q CHOCO CASHW 52 G</t>
   </si>
   <si>
     <t>20140016</t>
@@ -253,21 +253,15 @@
     <t>KINDER JOY DC COMICS</t>
   </si>
   <si>
-    <t>20140012</t>
-  </si>
-  <si>
-    <t>KITKAT CHNKY MILO 38</t>
+    <t>20139949</t>
+  </si>
+  <si>
+    <t>LMNILO CRNCHY CHO 18</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>20139949</t>
-  </si>
-  <si>
-    <t>LMNILO CRNCHY CHO 18</t>
-  </si>
-  <si>
     <t>20129814</t>
   </si>
   <si>
@@ -389,9 +383,6 @@
   </si>
   <si>
     <t>FSHRMANS COLA 25</t>
-  </si>
-  <si>
-    <t>,(E-1B)</t>
   </si>
   <si>
     <t>20132839</t>
@@ -973,7 +964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1678,7 +1669,7 @@
         <v>82</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1698,7 +1689,7 @@
         <v>82</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1718,7 +1709,7 @@
         <v>82</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1738,7 +1729,7 @@
         <v>82</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1755,10 +1746,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1766,19 +1757,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -1795,10 +1786,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -1815,10 +1806,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -1835,10 +1826,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -1855,10 +1846,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -1866,19 +1857,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -1895,10 +1886,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -1915,10 +1906,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -1935,10 +1926,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -1946,19 +1937,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -1975,10 +1966,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -1995,10 +1986,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2015,10 +2006,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2035,10 +2026,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2055,10 +2046,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2075,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2095,10 +2086,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>75</v>
@@ -2106,19 +2097,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>75</v>
@@ -2126,39 +2117,39 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2166,19 +2157,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="E60" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2195,10 +2186,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2206,19 +2197,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2226,19 +2217,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2246,19 +2237,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2266,19 +2257,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2286,19 +2277,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2315,10 +2306,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2326,19 +2317,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2346,19 +2337,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2366,19 +2357,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2395,10 +2386,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2406,22 +2397,22 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2435,13 +2426,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2455,93 +2446,93 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>167</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2555,10 +2546,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2566,19 +2557,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2586,19 +2577,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2606,41 +2597,21 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F83" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="188">
   <si>
     <t/>
   </si>
@@ -109,7 +109,7 @@
     <t>10003485</t>
   </si>
   <si>
-    <t>S/Q CHOCO ALMND 52 G</t>
+    <t>S/Q CHOCO ALMOND 52G</t>
   </si>
   <si>
     <t>5</t>
@@ -118,7 +118,7 @@
     <t>10036987</t>
   </si>
   <si>
-    <t>S/Q CHOCO CASHW 52 G</t>
+    <t>S/Q CHOCO CASHEW 52G</t>
   </si>
   <si>
     <t>20140016</t>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>LARIST CHOCO EGG 20G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>20135198</t>
@@ -1732,21 +1735,21 @@
         <v>33</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>4</v>
@@ -1757,16 +1760,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>8</v>
@@ -1777,16 +1780,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>11</v>
@@ -1797,16 +1800,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>14</v>
@@ -1817,16 +1820,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>33</v>
@@ -1837,16 +1840,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>4</v>
@@ -1857,16 +1860,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>8</v>
@@ -1877,16 +1880,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>11</v>
@@ -1897,16 +1900,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>14</v>
@@ -1917,16 +1920,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>4</v>
@@ -1937,16 +1940,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>8</v>
@@ -1957,16 +1960,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>11</v>
@@ -1977,16 +1980,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>14</v>
@@ -1997,16 +2000,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>33</v>
@@ -2017,16 +2020,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>38</v>
@@ -2037,16 +2040,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>45</v>
@@ -2057,16 +2060,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>4</v>
@@ -2077,16 +2080,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>8</v>
@@ -2097,16 +2100,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>11</v>
@@ -2117,16 +2120,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>14</v>
@@ -2137,16 +2140,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>33</v>
@@ -2157,16 +2160,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>4</v>
@@ -2177,16 +2180,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>8</v>
@@ -2197,16 +2200,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>11</v>
@@ -2217,16 +2220,16 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>14</v>
@@ -2237,16 +2240,16 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>33</v>
@@ -2257,16 +2260,16 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>38</v>
@@ -2277,16 +2280,16 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>4</v>
@@ -2297,16 +2300,16 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>8</v>
@@ -2317,16 +2320,16 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>11</v>
@@ -2337,16 +2340,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>14</v>
@@ -2357,16 +2360,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>4</v>
@@ -2377,16 +2380,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>8</v>
@@ -2397,136 +2400,136 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>4</v>
@@ -2537,16 +2540,16 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>8</v>
@@ -2557,16 +2560,16 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>11</v>
@@ -2577,16 +2580,16 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>14</v>
@@ -2597,16 +2600,16 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>33</v>

--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -385,7 +385,7 @@
     <t>20142507</t>
   </si>
   <si>
-    <t>FSHRMANS COLA 25</t>
+    <t>FSHRMANS COLA 22</t>
   </si>
   <si>
     <t>20132839</t>

--- a/COC04.xlsx
+++ b/COC04.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="186">
   <si>
     <t/>
   </si>
@@ -421,19 +421,13 @@
     <t>JLO PERMEN LIPSTICK</t>
   </si>
   <si>
-    <t>20139393</t>
-  </si>
-  <si>
-    <t>CC B.BABOL RASPBR 20</t>
+    <t>10004501</t>
+  </si>
+  <si>
+    <t>CC BIG BABOL BLUE20</t>
   </si>
   <si>
     <t>16</t>
-  </si>
-  <si>
-    <t>10004501</t>
-  </si>
-  <si>
-    <t>CC BIG BABOL BLUE20</t>
   </si>
   <si>
     <t>20122906</t>
@@ -967,7 +961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2172,7 +2166,7 @@
         <v>138</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2192,7 +2186,7 @@
         <v>138</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2212,7 +2206,7 @@
         <v>138</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2232,7 +2226,7 @@
         <v>138</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2252,7 +2246,7 @@
         <v>138</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2269,10 +2263,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2280,19 +2274,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2309,10 +2303,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2329,10 +2323,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2349,10 +2343,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2360,19 +2354,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2389,53 +2383,53 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="E73" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2449,13 +2443,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2469,13 +2463,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2489,13 +2483,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2509,30 +2503,30 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>165</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2549,10 +2543,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2569,10 +2563,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2589,32 +2583,12 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F82" s="1" t="s">
         <v>5</v>
       </c>
     </row>
